--- a/output/StructureDefinition-BRProblemaDiagnostico.xlsx
+++ b/output/StructureDefinition-BRProblemaDiagnostico.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3822" uniqueCount="569">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3820" uniqueCount="577">
   <si>
     <t>Property</t>
   </si>
@@ -1054,6 +1054,15 @@
     <t>gender</t>
   </si>
   <si>
+    <t>Sexo</t>
+  </si>
+  <si>
+    <t>Sexo biológico obtido por meio de exame clínico ou de outros métodos diagnósticos referente ao indivíduo da hipótese de impossibilidade de identificação.</t>
+  </si>
+  <si>
+    <t>http://www.saude.gov.br/fhir/r4/ValueSet/BRSexo-1.0</t>
+  </si>
+  <si>
     <t>Condition.subject.extension:unidentifiedPatient.extension:gender.id</t>
   </si>
   <si>
@@ -1103,6 +1112,12 @@
   </si>
   <si>
     <t>birthYear</t>
+  </si>
+  <si>
+    <t>Ano de nascimento estimado</t>
+  </si>
+  <si>
+    <t>Estimativa do ano de nascimento por meio de observação direta da idade do indivíduo na hipótese de impossibilidade de identificação..</t>
   </si>
   <si>
     <t>Condition.subject.extension:unidentifiedPatient.extension:birthYear.id</t>
@@ -1125,6 +1140,15 @@
   </si>
   <si>
     <t>reason</t>
+  </si>
+  <si>
+    <t>Justificativa da impossibilidade de identificação do indivíduo</t>
+  </si>
+  <si>
+    <t>Razão pela qual não foi possível obter os dados de identificação do indivíduo no contato assistencial.</t>
+  </si>
+  <si>
+    <t>http://www.saude.gov.br/fhir/r4/ValueSet/BRJustificativaIndividuoNaoIdentificado-1.0</t>
   </si>
   <si>
     <t>Condition.subject.extension:unidentifiedPatient.extension:reason.id</t>
@@ -7595,10 +7619,10 @@
         <v>137</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>316</v>
+        <v>331</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>317</v>
+        <v>332</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7625,13 +7649,11 @@
         <v>79</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y46" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="Y46" s="2"/>
       <c r="Z46" t="s" s="2">
-        <v>79</v>
+        <v>333</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>79</v>
@@ -7684,10 +7706,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7802,10 +7824,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7922,10 +7944,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7951,13 +7973,13 @@
         <v>105</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -8007,7 +8029,7 @@
         <v>79</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>92</v>
@@ -8042,10 +8064,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8071,10 +8093,10 @@
         <v>111</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -8125,7 +8147,7 @@
         <v>79</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8160,13 +8182,13 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="B51" t="s" s="2">
         <v>326</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="D51" t="s" s="2">
         <v>79</v>
@@ -8191,10 +8213,10 @@
         <v>137</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>316</v>
+        <v>351</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>317</v>
+        <v>352</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8280,10 +8302,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8398,10 +8420,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8518,10 +8540,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8547,13 +8569,13 @@
         <v>105</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8561,7 +8583,7 @@
       </c>
       <c r="Q54" s="2"/>
       <c r="R54" t="s" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="S54" t="s" s="2">
         <v>79</v>
@@ -8603,7 +8625,7 @@
         <v>79</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>92</v>
@@ -8638,10 +8660,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8664,13 +8686,13 @@
         <v>79</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8721,7 +8743,7 @@
         <v>79</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8756,13 +8778,13 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="B56" t="s" s="2">
         <v>326</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="D56" t="s" s="2">
         <v>79</v>
@@ -8787,10 +8809,10 @@
         <v>137</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>316</v>
+        <v>360</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>317</v>
+        <v>361</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8817,13 +8839,11 @@
         <v>79</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y56" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="Y56" s="2"/>
       <c r="Z56" t="s" s="2">
-        <v>79</v>
+        <v>362</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>79</v>
@@ -8876,10 +8896,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8994,10 +9014,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9114,10 +9134,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9143,13 +9163,13 @@
         <v>105</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9157,7 +9177,7 @@
       </c>
       <c r="Q59" s="2"/>
       <c r="R59" t="s" s="2">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="S59" t="s" s="2">
         <v>79</v>
@@ -9199,7 +9219,7 @@
         <v>79</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>92</v>
@@ -9234,10 +9254,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9263,10 +9283,10 @@
         <v>158</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9317,7 +9337,7 @@
         <v>79</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9352,13 +9372,13 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="B61" t="s" s="2">
         <v>326</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="D61" t="s" s="2">
         <v>79</v>
@@ -9368,7 +9388,7 @@
         <v>80</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>328</v>
+        <v>81</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>82</v>
@@ -9472,10 +9492,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9501,13 +9521,13 @@
         <v>105</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -9515,7 +9535,7 @@
       </c>
       <c r="Q62" s="2"/>
       <c r="R62" t="s" s="2">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="S62" t="s" s="2">
         <v>79</v>
@@ -9557,7 +9577,7 @@
         <v>79</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>92</v>
@@ -9592,10 +9612,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9618,13 +9638,13 @@
         <v>79</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9675,7 +9695,7 @@
         <v>79</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9710,10 +9730,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9739,13 +9759,13 @@
         <v>172</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9795,7 +9815,7 @@
         <v>79</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9804,7 +9824,7 @@
         <v>92</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="AJ64" t="s" s="2">
         <v>103</v>
@@ -9830,10 +9850,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9859,13 +9879,13 @@
         <v>105</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9873,7 +9893,7 @@
       </c>
       <c r="Q65" s="2"/>
       <c r="R65" t="s" s="2">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="S65" t="s" s="2">
         <v>79</v>
@@ -9891,13 +9911,13 @@
         <v>79</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>79</v>
@@ -9915,7 +9935,7 @@
         <v>79</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -9950,10 +9970,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9979,13 +9999,13 @@
         <v>149</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -10035,7 +10055,7 @@
         <v>79</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10059,7 +10079,7 @@
         <v>79</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>79</v>
@@ -10070,10 +10090,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10188,10 +10208,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10308,10 +10328,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10337,16 +10357,16 @@
         <v>111</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>79</v>
@@ -10374,10 +10394,10 @@
         <v>162</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>396</v>
+        <v>404</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>79</v>
@@ -10395,7 +10415,7 @@
         <v>79</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10419,7 +10439,7 @@
         <v>134</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>398</v>
+        <v>406</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>79</v>
@@ -10430,10 +10450,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10459,16 +10479,16 @@
         <v>158</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>79</v>
@@ -10493,13 +10513,13 @@
         <v>79</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>405</v>
+        <v>413</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>79</v>
@@ -10517,7 +10537,7 @@
         <v>79</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10538,10 +10558,10 @@
         <v>79</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>407</v>
+        <v>415</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>398</v>
+        <v>406</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>79</v>
@@ -10552,10 +10572,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10581,16 +10601,16 @@
         <v>105</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>410</v>
+        <v>418</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>79</v>
@@ -10603,7 +10623,7 @@
         <v>79</v>
       </c>
       <c r="T71" t="s" s="2">
-        <v>413</v>
+        <v>421</v>
       </c>
       <c r="U71" t="s" s="2">
         <v>79</v>
@@ -10639,7 +10659,7 @@
         <v>79</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10660,10 +10680,10 @@
         <v>79</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>79</v>
@@ -10674,10 +10694,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10703,13 +10723,13 @@
         <v>172</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>418</v>
+        <v>426</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10723,7 +10743,7 @@
         <v>79</v>
       </c>
       <c r="T72" t="s" s="2">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="U72" t="s" s="2">
         <v>79</v>
@@ -10759,7 +10779,7 @@
         <v>79</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -10780,10 +10800,10 @@
         <v>79</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>423</v>
+        <v>431</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>424</v>
+        <v>432</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>79</v>
@@ -10794,10 +10814,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>425</v>
+        <v>433</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>425</v>
+        <v>433</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10820,13 +10840,13 @@
         <v>82</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>427</v>
+        <v>435</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>428</v>
+        <v>436</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10877,7 +10897,7 @@
         <v>79</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -10898,10 +10918,10 @@
         <v>79</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>430</v>
+        <v>438</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>431</v>
+        <v>439</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>79</v>
@@ -10912,10 +10932,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>432</v>
+        <v>440</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>432</v>
+        <v>440</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10938,16 +10958,16 @@
         <v>82</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>433</v>
+        <v>441</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>434</v>
+        <v>442</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>435</v>
+        <v>443</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -10997,7 +11017,7 @@
         <v>79</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11018,10 +11038,10 @@
         <v>79</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>79</v>
@@ -11032,10 +11052,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11061,13 +11081,13 @@
         <v>172</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>442</v>
+        <v>450</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -11117,7 +11137,7 @@
         <v>79</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11152,10 +11172,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11178,16 +11198,16 @@
         <v>82</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>447</v>
+        <v>455</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>449</v>
+        <v>457</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -11237,7 +11257,7 @@
         <v>79</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11252,19 +11272,19 @@
         <v>103</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>450</v>
+        <v>458</v>
       </c>
       <c r="AL76" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="AP76" t="s" s="2">
         <v>79</v>
@@ -11272,10 +11292,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11298,16 +11318,16 @@
         <v>82</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>456</v>
+        <v>464</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -11357,7 +11377,7 @@
         <v>79</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11372,19 +11392,19 @@
         <v>103</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="AL77" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>460</v>
+        <v>468</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>462</v>
+        <v>470</v>
       </c>
       <c r="AP77" t="s" s="2">
         <v>79</v>
@@ -11392,10 +11412,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11418,16 +11438,16 @@
         <v>79</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>464</v>
+        <v>472</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>466</v>
+        <v>474</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -11477,7 +11497,7 @@
         <v>79</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11486,7 +11506,7 @@
         <v>92</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="AJ78" t="s" s="2">
         <v>103</v>
@@ -11501,10 +11521,10 @@
         <v>79</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>468</v>
+        <v>476</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="AP78" t="s" s="2">
         <v>79</v>
@@ -11512,10 +11532,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>470</v>
+        <v>478</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>470</v>
+        <v>478</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11538,13 +11558,13 @@
         <v>82</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>471</v>
+        <v>479</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>472</v>
+        <v>480</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>473</v>
+        <v>481</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -11595,7 +11615,7 @@
         <v>79</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>470</v>
+        <v>478</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -11616,13 +11636,13 @@
         <v>79</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>474</v>
+        <v>482</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>475</v>
+        <v>483</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>476</v>
+        <v>484</v>
       </c>
       <c r="AP79" t="s" s="2">
         <v>79</v>
@@ -11630,10 +11650,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>477</v>
+        <v>485</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>477</v>
+        <v>485</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11656,13 +11676,13 @@
         <v>82</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>478</v>
+        <v>486</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>479</v>
+        <v>487</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>480</v>
+        <v>488</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -11713,7 +11733,7 @@
         <v>79</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>477</v>
+        <v>485</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -11737,10 +11757,10 @@
         <v>79</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="AO80" t="s" s="2">
-        <v>482</v>
+        <v>490</v>
       </c>
       <c r="AP80" t="s" s="2">
         <v>79</v>
@@ -11748,10 +11768,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>483</v>
+        <v>491</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>483</v>
+        <v>491</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11774,13 +11794,13 @@
         <v>82</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>478</v>
+        <v>486</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>484</v>
+        <v>492</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -11831,7 +11851,7 @@
         <v>79</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>483</v>
+        <v>491</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -11852,13 +11872,13 @@
         <v>79</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>486</v>
+        <v>494</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>487</v>
+        <v>495</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>488</v>
+        <v>496</v>
       </c>
       <c r="AP81" t="s" s="2">
         <v>79</v>
@@ -11866,10 +11886,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>489</v>
+        <v>497</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>489</v>
+        <v>497</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11892,13 +11912,13 @@
         <v>79</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>490</v>
+        <v>498</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>491</v>
+        <v>499</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>492</v>
+        <v>500</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -11949,7 +11969,7 @@
         <v>79</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>489</v>
+        <v>497</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -11961,7 +11981,7 @@
         <v>79</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>493</v>
+        <v>501</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>79</v>
@@ -11973,7 +11993,7 @@
         <v>79</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>494</v>
+        <v>502</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>79</v>
@@ -11984,10 +12004,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12102,10 +12122,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>496</v>
+        <v>504</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>496</v>
+        <v>504</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12222,14 +12242,14 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>497</v>
+        <v>505</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>497</v>
+        <v>505</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>498</v>
+        <v>506</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
@@ -12251,10 +12271,10 @@
         <v>137</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>499</v>
+        <v>507</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>500</v>
+        <v>508</v>
       </c>
       <c r="N85" t="s" s="2">
         <v>140</v>
@@ -12309,7 +12329,7 @@
         <v>79</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>501</v>
+        <v>509</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12344,10 +12364,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>502</v>
+        <v>510</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>502</v>
+        <v>510</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12373,10 +12393,10 @@
         <v>158</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>503</v>
+        <v>511</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>504</v>
+        <v>512</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -12406,10 +12426,10 @@
         <v>298</v>
       </c>
       <c r="Y86" t="s" s="2">
-        <v>505</v>
+        <v>513</v>
       </c>
       <c r="Z86" t="s" s="2">
-        <v>506</v>
+        <v>514</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>79</v>
@@ -12427,7 +12447,7 @@
         <v>79</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>502</v>
+        <v>510</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -12436,7 +12456,7 @@
         <v>92</v>
       </c>
       <c r="AI86" t="s" s="2">
-        <v>507</v>
+        <v>515</v>
       </c>
       <c r="AJ86" t="s" s="2">
         <v>103</v>
@@ -12445,7 +12465,7 @@
         <v>79</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>508</v>
+        <v>516</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>168</v>
@@ -12462,10 +12482,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>509</v>
+        <v>517</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>509</v>
+        <v>517</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12488,13 +12508,13 @@
         <v>79</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>510</v>
+        <v>518</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>512</v>
+        <v>520</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -12545,7 +12565,7 @@
         <v>79</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>509</v>
+        <v>517</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -12554,7 +12574,7 @@
         <v>81</v>
       </c>
       <c r="AI87" t="s" s="2">
-        <v>507</v>
+        <v>515</v>
       </c>
       <c r="AJ87" t="s" s="2">
         <v>103</v>
@@ -12569,7 +12589,7 @@
         <v>79</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>513</v>
+        <v>521</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>79</v>
@@ -12580,10 +12600,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>514</v>
+        <v>522</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>514</v>
+        <v>522</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12609,10 +12629,10 @@
         <v>158</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>515</v>
+        <v>523</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>516</v>
+        <v>524</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -12642,10 +12662,10 @@
         <v>298</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>517</v>
+        <v>525</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>518</v>
+        <v>526</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>79</v>
@@ -12663,7 +12683,7 @@
         <v>79</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>514</v>
+        <v>522</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -12687,7 +12707,7 @@
         <v>79</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>79</v>
@@ -12698,10 +12718,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>520</v>
+        <v>528</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>520</v>
+        <v>528</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12724,16 +12744,16 @@
         <v>79</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>490</v>
+        <v>498</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>521</v>
+        <v>529</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>522</v>
+        <v>530</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>523</v>
+        <v>531</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -12783,7 +12803,7 @@
         <v>79</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>520</v>
+        <v>528</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -12795,7 +12815,7 @@
         <v>79</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>524</v>
+        <v>532</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>79</v>
@@ -12807,7 +12827,7 @@
         <v>79</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>525</v>
+        <v>533</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>79</v>
@@ -12818,10 +12838,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>526</v>
+        <v>534</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>526</v>
+        <v>534</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12936,10 +12956,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>527</v>
+        <v>535</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>527</v>
+        <v>535</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13056,14 +13076,14 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>528</v>
+        <v>536</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>528</v>
+        <v>536</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>498</v>
+        <v>506</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
@@ -13085,10 +13105,10 @@
         <v>137</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>499</v>
+        <v>507</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>500</v>
+        <v>508</v>
       </c>
       <c r="N92" t="s" s="2">
         <v>140</v>
@@ -13143,7 +13163,7 @@
         <v>79</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>501</v>
+        <v>509</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13178,10 +13198,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>529</v>
+        <v>537</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>529</v>
+        <v>537</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13207,10 +13227,10 @@
         <v>158</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>530</v>
+        <v>538</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>531</v>
+        <v>539</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -13240,10 +13260,10 @@
         <v>298</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>532</v>
+        <v>540</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>533</v>
+        <v>541</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>79</v>
@@ -13261,7 +13281,7 @@
         <v>79</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>529</v>
+        <v>537</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13270,13 +13290,13 @@
         <v>81</v>
       </c>
       <c r="AI93" t="s" s="2">
-        <v>534</v>
+        <v>542</v>
       </c>
       <c r="AJ93" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>535</v>
+        <v>543</v>
       </c>
       <c r="AL93" t="s" s="2">
         <v>257</v>
@@ -13285,10 +13305,10 @@
         <v>79</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>536</v>
+        <v>544</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="AP93" t="s" s="2">
         <v>79</v>
@@ -13296,10 +13316,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>538</v>
+        <v>546</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>538</v>
+        <v>546</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13322,13 +13342,13 @@
         <v>82</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>539</v>
+        <v>547</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>540</v>
+        <v>548</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>541</v>
+        <v>549</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -13379,7 +13399,7 @@
         <v>79</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>538</v>
+        <v>546</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13388,7 +13408,7 @@
         <v>81</v>
       </c>
       <c r="AI94" t="s" s="2">
-        <v>534</v>
+        <v>542</v>
       </c>
       <c r="AJ94" t="s" s="2">
         <v>103</v>
@@ -13403,10 +13423,10 @@
         <v>79</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>513</v>
+        <v>521</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="AP94" t="s" s="2">
         <v>79</v>
@@ -13414,10 +13434,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>542</v>
+        <v>550</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>542</v>
+        <v>550</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13440,13 +13460,13 @@
         <v>79</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>543</v>
+        <v>551</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>544</v>
+        <v>552</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>545</v>
+        <v>553</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -13497,7 +13517,7 @@
         <v>79</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>542</v>
+        <v>550</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -13512,16 +13532,16 @@
         <v>103</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>546</v>
+        <v>554</v>
       </c>
       <c r="AL95" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>547</v>
+        <v>555</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>548</v>
+        <v>556</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>79</v>
@@ -13532,10 +13552,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>549</v>
+        <v>557</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>549</v>
+        <v>557</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13650,10 +13670,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>550</v>
+        <v>558</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>550</v>
+        <v>558</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13770,10 +13790,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>551</v>
+        <v>559</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>551</v>
+        <v>559</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13796,16 +13816,16 @@
         <v>82</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>552</v>
+        <v>560</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>553</v>
+        <v>561</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>554</v>
+        <v>562</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>555</v>
+        <v>563</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -13855,7 +13875,7 @@
         <v>79</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>556</v>
+        <v>564</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -13879,7 +13899,7 @@
         <v>134</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>557</v>
+        <v>565</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>79</v>
@@ -13890,10 +13910,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>558</v>
+        <v>566</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>558</v>
+        <v>566</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13916,13 +13936,13 @@
         <v>82</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>471</v>
+        <v>479</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>559</v>
+        <v>567</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>560</v>
+        <v>568</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -13973,7 +13993,7 @@
         <v>79</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>561</v>
+        <v>569</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -13997,7 +14017,7 @@
         <v>134</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>562</v>
+        <v>570</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>79</v>
@@ -14008,10 +14028,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>563</v>
+        <v>571</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>563</v>
+        <v>571</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14034,13 +14054,13 @@
         <v>82</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>564</v>
+        <v>572</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>565</v>
+        <v>573</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>566</v>
+        <v>574</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -14091,7 +14111,7 @@
         <v>79</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>567</v>
+        <v>575</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>92</v>
@@ -14115,7 +14135,7 @@
         <v>134</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>568</v>
+        <v>576</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>79</v>
